--- a/research/runs/20260302-070309-excel-formula-language-pass2-pack-01/fixtures/formula_parse_pass2/FMLP2-022.xlsx
+++ b/research/runs/20260302-070309-excel-formula-language-pass2-pack-01/fixtures/formula_parse_pass2/FMLP2-022.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\DnaCalc\Foundation\research\runs\20260302-070309-excel-formula-language-pass2-pack-01\fixtures\formula_parse_pass2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BDCFF3-CF8C-4256-BC50-B375AF4F0A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BFCC81-B1F7-4D4F-8029-A24864D60352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3135" yWindow="3885" windowWidth="11955" windowHeight="11595" xr2:uid="{C57E98EB-85E5-43DA-BD38-4DBAA5262617}"/>
+    <workbookView xWindow="3135" yWindow="3885" windowWidth="11955" windowHeight="11595" xr2:uid="{897056C3-5A53-42D3-A740-7E11BAC69FFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -417,7 +417,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4615CC7-C14D-4FE7-BF3A-601C46C19BBF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E3B8279-54FE-4A05-976A-D2AF03BD07E2}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/research/runs/20260302-070309-excel-formula-language-pass2-pack-01/fixtures/formula_parse_pass2/FMLP2-022.xlsx
+++ b/research/runs/20260302-070309-excel-formula-language-pass2-pack-01/fixtures/formula_parse_pass2/FMLP2-022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\DnaCalc\Foundation\research\runs\20260302-070309-excel-formula-language-pass2-pack-01\fixtures\formula_parse_pass2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BFCC81-B1F7-4D4F-8029-A24864D60352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBEB3FDE-2469-4DA7-93FC-EAEE3481B50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3135" yWindow="3885" windowWidth="11955" windowHeight="11595" xr2:uid="{897056C3-5A53-42D3-A740-7E11BAC69FFF}"/>
   </bookViews>
